--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 3 - РАЗХОД ПО ПРОЕКТ ОИЦ ВАРНА/ОБЩИНА ВАРНА % 3 - РАЗХОД ПО ПРОЕКТ ОИЦ ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 3 - РАЗХОД ПО ПРОЕКТ ОИЦ ВАРНА/ОБЩИНА ВАРНА % 3 - РАЗХОД ПО ПРОЕКТ ОИЦ ВАРНА.xlsx
@@ -131,7 +131,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -141,12 +141,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -197,17 +191,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
